--- a/data/trans_dic/P79$ninguna_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P79$ninguna_2023-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>83,66%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>82,78; 93,39</t>
+          <t>78,88; 90,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>73,92; 86,89</t>
+          <t>74,65; 86,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>81,17; 89,54</t>
+          <t>79,13; 87,43</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>84,99%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>80,16; 88,88</t>
+          <t>81,52; 89,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>80,99; 88,16</t>
+          <t>80,61; 87,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82,3; 87,74</t>
+          <t>82,04; 87,56</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>85,65%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>81,9; 88,28</t>
+          <t>81,24; 87,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85,52; 91,35</t>
+          <t>83,92; 88,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>84,6; 88,86</t>
+          <t>83,58; 87,57</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>85,96%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>85,55; 96,0</t>
+          <t>82,1; 88,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>85,88; 90,34</t>
+          <t>84,31; 88,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>86,77; 93,75</t>
+          <t>84,18; 87,65</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>84,58%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>82,79; 88,26</t>
+          <t>81,68; 87,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>82,01; 87,04</t>
+          <t>81,62; 86,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>83,31; 87,09</t>
+          <t>82,63; 86,42</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>87,78%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>85,6; 90,76</t>
+          <t>85,12; 90,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>87,22; 97,09</t>
+          <t>84,9; 89,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>87,33; 95,35</t>
+          <t>85,97; 89,53</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,15%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>86,3; 91,9</t>
+          <t>86,29; 91,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>85,6; 90,24</t>
+          <t>84,93; 89,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>86,73; 90,42</t>
+          <t>86,22; 89,72</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>85,75%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>86,06; 90,44</t>
+          <t>84,61; 87,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>86,01; 89,4</t>
+          <t>84,46; 86,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>86,36; 89,15</t>
+          <t>84,93; 86,58</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>330860</t>
+          <t>324045</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>235562</t>
+          <t>274398</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>566422</t>
+          <t>598443</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>306582; 345906</t>
+          <t>298199; 342301</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>213917; 251475</t>
+          <t>251810; 292362</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>535571; 590741</t>
+          <t>566087; 625474</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>356444</t>
+          <t>401778</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>364947</t>
+          <t>408727</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>721391</t>
+          <t>810505</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>333526; 369816</t>
+          <t>382519; 419473</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>348266; 379088</t>
+          <t>390436; 423694</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>696289; 742351</t>
+          <t>782382; 834972</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>445775</t>
+          <t>507502</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>509212</t>
+          <t>524359</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>954987</t>
+          <t>1031861</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>428602; 462010</t>
+          <t>487184; 524383</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>493785; 527433</t>
+          <t>507742; 536908</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>931190; 978120</t>
+          <t>1006917; 1054938</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>789054</t>
+          <t>583278</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>611763</t>
+          <t>619711</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1400818</t>
+          <t>1202989</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>746587; 837743</t>
+          <t>560277; 602218</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>596953; 627946</t>
+          <t>604564; 633606</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1360430; 1469829</t>
+          <t>1178099; 1226746</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>466364</t>
+          <t>502094</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>445855</t>
+          <t>493647</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>912218</t>
+          <t>995741</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>450763; 480545</t>
+          <t>482535; 517224</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>431226; 457684</t>
+          <t>478734; 506438</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>891668; 932174</t>
+          <t>972838; 1017370</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>317529</t>
+          <t>349417</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>549682</t>
+          <t>372927</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>867211</t>
+          <t>722343</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>308075; 326646</t>
+          <t>337546; 358892</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>520935; 579860</t>
+          <t>362014; 383106</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>835845; 912629</t>
+          <t>707490; 736791</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>247863</t>
+          <t>271517</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>357300</t>
+          <t>386448</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>605164</t>
+          <t>657965</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>239276; 254800</t>
+          <t>262407; 279426</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>347687; 366530</t>
+          <t>375643; 396966</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>592731; 617929</t>
+          <t>643589; 669700</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2953890</t>
+          <t>2939631</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3074321</t>
+          <t>3080217</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6028210</t>
+          <t>6019848</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2895118; 3042585</t>
+          <t>2894495; 2985086</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3028389; 3148028</t>
+          <t>3039780; 3117324</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5945894; 6138405</t>
+          <t>5961646; 6077518</t>
         </is>
       </c>
     </row>
